--- a/01_Reporting_Suite/DAILY_SUMMARY.xlsx
+++ b/01_Reporting_Suite/DAILY_SUMMARY.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>PROJECT SCHEDULE</t>
   </si>
@@ -33,10 +33,10 @@
     <t>Gladstone k2 2026 Shutdown</t>
   </si>
   <si>
-    <t>13/07/2026 05:42 AM</t>
-  </si>
-  <si>
-    <t>29/07/2026 05:42 AM</t>
+    <t>13/07/2026 09:33 AM</t>
+  </si>
+  <si>
+    <t>30/07/2026 09:33 AM</t>
   </si>
   <si>
     <t>Andrew Fisher</t>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t>TOTAL FOR: 27/07/2026</t>
+  </si>
+  <si>
+    <t>TOTAL FOR: 28/07/2026</t>
+  </si>
+  <si>
+    <t>TOTAL FOR: 29/07/2026</t>
   </si>
   <si>
     <t>REPORT TOTAL:</t>
@@ -214,14 +220,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.6638088226318" customWidth="1"/>
     <col min="2" max="2" width="9.6135892868042" customWidth="1"/>
     <col min="3" max="3" width="12.0372314453125" customWidth="1"/>
     <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.6135892868042" customWidth="1"/>
     <col min="6" max="6" width="13.991286277771" customWidth="1"/>
     <col min="7" max="7" width="9.50002956390381" customWidth="1"/>
     <col min="8" max="8" width="9.96756935119629" customWidth="1"/>
@@ -770,40 +776,122 @@
         <v>34</v>
       </c>
       <c r="B14" s="0">
-        <v>74931.57</v>
+        <v>10397.13</v>
       </c>
       <c r="C14" s="0">
-        <v>45000</v>
+        <v>1134</v>
       </c>
       <c r="D14" s="0">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0">
+        <v>4032.07</v>
+      </c>
+      <c r="F14" s="0">
+        <v>0</v>
+      </c>
+      <c r="G14" s="0">
+        <v>0</v>
+      </c>
+      <c r="H14" s="0">
+        <v>0</v>
+      </c>
+      <c r="I14" s="0">
+        <v>0</v>
+      </c>
+      <c r="J14" s="0">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0">
+        <v>0</v>
+      </c>
+      <c r="L14" s="0">
+        <v>0</v>
+      </c>
+      <c r="M14" s="0">
+        <v>15563.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="0">
+        <v>11180.75</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0</v>
+      </c>
+      <c r="E15" s="0">
+        <v>0</v>
+      </c>
+      <c r="F15" s="0">
+        <v>0</v>
+      </c>
+      <c r="G15" s="0">
+        <v>0</v>
+      </c>
+      <c r="H15" s="0">
+        <v>0</v>
+      </c>
+      <c r="I15" s="0">
+        <v>0</v>
+      </c>
+      <c r="J15" s="0">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0">
+        <v>0</v>
+      </c>
+      <c r="L15" s="0">
+        <v>0</v>
+      </c>
+      <c r="M15" s="0">
+        <v>11180.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="0">
+        <v>96509.45</v>
+      </c>
+      <c r="C16" s="0">
+        <v>46134</v>
+      </c>
+      <c r="D16" s="0">
         <v>58520</v>
       </c>
-      <c r="E14" s="0">
-        <v>15605</v>
-      </c>
-      <c r="F14" s="0">
-        <v>0</v>
-      </c>
-      <c r="G14" s="0">
-        <v>0</v>
-      </c>
-      <c r="H14" s="0">
-        <v>0</v>
-      </c>
-      <c r="I14" s="0">
-        <v>0</v>
-      </c>
-      <c r="J14" s="0">
-        <v>0</v>
-      </c>
-      <c r="K14" s="0">
-        <v>0</v>
-      </c>
-      <c r="L14" s="0">
-        <v>0</v>
-      </c>
-      <c r="M14" s="0">
-        <v>194056.57</v>
+      <c r="E16" s="0">
+        <v>19637.07</v>
+      </c>
+      <c r="F16" s="0">
+        <v>0</v>
+      </c>
+      <c r="G16" s="0">
+        <v>0</v>
+      </c>
+      <c r="H16" s="0">
+        <v>0</v>
+      </c>
+      <c r="I16" s="0">
+        <v>0</v>
+      </c>
+      <c r="J16" s="0">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0">
+        <v>0</v>
+      </c>
+      <c r="L16" s="0">
+        <v>0</v>
+      </c>
+      <c r="M16" s="0">
+        <v>220800.52</v>
       </c>
     </row>
   </sheetData>
